--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127129460</v>
+        <v>127134154</v>
       </c>
       <c r="B4" t="n">
         <v>57657</v>
@@ -913,21 +913,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596559</v>
+        <v>596668</v>
       </c>
       <c r="R4" t="n">
-        <v>6985775</v>
+        <v>6985712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127134154</v>
+        <v>127129460</v>
       </c>
       <c r="B5" t="n">
         <v>57657</v>
@@ -1020,16 +1015,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596668</v>
+        <v>596559</v>
       </c>
       <c r="R5" t="n">
-        <v>6985712</v>
+        <v>6985775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127134153</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127128081</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127134154</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129460</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127128137</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127129567</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127129529</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>127128181</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127134153</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127128081</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127134154</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129460</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127128137</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127129567</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127129529</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>127128181</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127134153</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127128081</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127134154</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129460</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127128137</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127129567</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>127129529</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>127128181</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127134153</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127128081</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127134154</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127129460</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>127128137</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127129567</v>
+        <v>127129529</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596524</v>
+        <v>596547</v>
       </c>
       <c r="R7" t="n">
-        <v>6985880</v>
+        <v>6985835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127129529</v>
+        <v>127129567</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596547</v>
+        <v>596524</v>
       </c>
       <c r="R8" t="n">
-        <v>6985835</v>
+        <v>6985880</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
         <v>127128181</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127134153</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127128081</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127134154</v>
+        <v>127129460</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +913,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596668</v>
+        <v>596559</v>
       </c>
       <c r="R4" t="n">
-        <v>6985712</v>
+        <v>6985775</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,17 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127129460</v>
+        <v>127134154</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1020,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596559</v>
+        <v>596668</v>
       </c>
       <c r="R5" t="n">
-        <v>6985775</v>
+        <v>6985712</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1096,7 @@
         <v>127128137</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127129529</v>
+        <v>127129567</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596547</v>
+        <v>596524</v>
       </c>
       <c r="R7" t="n">
-        <v>6985835</v>
+        <v>6985880</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127129567</v>
+        <v>127129529</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596524</v>
+        <v>596547</v>
       </c>
       <c r="R8" t="n">
-        <v>6985880</v>
+        <v>6985835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
         <v>127128181</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127134153</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127128081</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127129460</v>
+        <v>127134154</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +913,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596559</v>
+        <v>596668</v>
       </c>
       <c r="R4" t="n">
-        <v>6985775</v>
+        <v>6985712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127134154</v>
+        <v>127129460</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,16 +1015,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596668</v>
+        <v>596559</v>
       </c>
       <c r="R5" t="n">
-        <v>6985712</v>
+        <v>6985775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1096,7 @@
         <v>127128137</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127129567</v>
+        <v>127129529</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596524</v>
+        <v>596547</v>
       </c>
       <c r="R7" t="n">
-        <v>6985880</v>
+        <v>6985835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127129529</v>
+        <v>127129567</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596547</v>
+        <v>596524</v>
       </c>
       <c r="R8" t="n">
-        <v>6985835</v>
+        <v>6985880</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
         <v>127128181</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127134153</v>
+        <v>127128081</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,16 +704,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596565</v>
+        <v>596451</v>
       </c>
       <c r="R2" t="n">
-        <v>6985774</v>
+        <v>6985990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128081</v>
+        <v>127128137</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596451</v>
+        <v>596484</v>
       </c>
       <c r="R3" t="n">
-        <v>6985990</v>
+        <v>6985964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127134154</v>
+        <v>127128181</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +918,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596668</v>
+        <v>596478</v>
       </c>
       <c r="R4" t="n">
-        <v>6985712</v>
+        <v>6985936</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,17 +959,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127129460</v>
+        <v>127128321</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596559</v>
+        <v>596539</v>
       </c>
       <c r="R5" t="n">
-        <v>6985775</v>
+        <v>6985943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128137</v>
+        <v>127128987</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596484</v>
+        <v>596549</v>
       </c>
       <c r="R6" t="n">
-        <v>6985964</v>
+        <v>6985713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127129529</v>
+        <v>127129460</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596547</v>
+        <v>596559</v>
       </c>
       <c r="R7" t="n">
-        <v>6985835</v>
+        <v>6985775</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127129567</v>
+        <v>127129529</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,7 +1348,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596524</v>
+        <v>596547</v>
       </c>
       <c r="R8" t="n">
-        <v>6985880</v>
+        <v>6985835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127128181</v>
+        <v>127129567</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596478</v>
+        <v>596524</v>
       </c>
       <c r="R9" t="n">
-        <v>6985936</v>
+        <v>6985880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,6 +1528,210 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127134153</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Risåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596565</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6985774</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127134154</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Risåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596668</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6985712</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22054-2025 artfynd.xlsx
+++ b/artfynd/A 22054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128081</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128137</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128181</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128321</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128987</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127129460</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127129529</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127129567</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127134153</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,8 +1782,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127134154</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>